--- a/Supply Chain Excel Workbook.xlsx
+++ b/Supply Chain Excel Workbook.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wingc\Downloads\Supply Chain Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3707136-1723-4007-ADF9-825ACE6EC205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5217F1B6-122C-4DF3-A2A1-B74355397827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ABCD Classification" sheetId="1" r:id="rId1"/>
-    <sheet name="Re-Order Point &amp; XLOOKUP" sheetId="2" r:id="rId2"/>
+    <sheet name="SKU Performance Pivot Table" sheetId="3" r:id="rId2"/>
+    <sheet name="Re-Order Point &amp; XLOOKUP" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="9" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="48">
   <si>
     <t>SKU / Item</t>
   </si>
@@ -174,14 +178,21 @@
   </si>
   <si>
     <t>XLOOKUP Search: Use SKU to Find Current Stock On Hand</t>
+  </si>
+  <si>
+    <t>Average of Total Profit</t>
+  </si>
+  <si>
+    <t>Average of Profit Per Unit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -243,7 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -257,12 +268,174 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="55">
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -280,16 +453,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -324,6 +487,551 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Wingchee W" refreshedDate="45991.28678159722" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="19" xr:uid="{879F5387-4519-4FE1-9C2D-BC6B8DF5E9C2}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G20" sheet="ABCD Classification"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="SKU / Item" numFmtId="0">
+      <sharedItems count="19">
+        <s v="SKU99012"/>
+        <s v="SKU22769"/>
+        <s v="SKU22001"/>
+        <s v="SKU33445"/>
+        <s v="SKU99008"/>
+        <s v="SKU67887"/>
+        <s v="SKU99009"/>
+        <s v="SKU45456"/>
+        <s v="SKU99014"/>
+        <s v="SKU99006"/>
+        <s v="SKU99013"/>
+        <s v="SKU99005"/>
+        <s v="SKU98633"/>
+        <s v="SKU00912"/>
+        <s v="SKU99010"/>
+        <s v="SKU99011"/>
+        <s v="SKU99007"/>
+        <s v="SKU78512"/>
+        <s v="SKU45667"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Profit Per Unit" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="25" maxValue="48"/>
+    </cacheField>
+    <cacheField name="Units Sold" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2691" maxValue="3905"/>
+    </cacheField>
+    <cacheField name="Total Profit" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="67275" maxValue="185040"/>
+    </cacheField>
+    <cacheField name="Sales Ranking" numFmtId="0">
+      <sharedItems count="3">
+        <s v="A"/>
+        <s v="C"/>
+        <s v="D"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Total Profit Ranking" numFmtId="0">
+      <sharedItems count="4">
+        <s v="A"/>
+        <s v="B"/>
+        <s v="D"/>
+        <s v="C"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Discontinue?" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="19">
+  <r>
+    <x v="0"/>
+    <n v="48"/>
+    <n v="3855"/>
+    <n v="185040"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="37"/>
+    <n v="3672"/>
+    <n v="135864"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="43"/>
+    <n v="3601"/>
+    <n v="154843"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="47"/>
+    <n v="3876"/>
+    <n v="182172"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="31"/>
+    <n v="3446"/>
+    <n v="106826"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="32"/>
+    <n v="3694"/>
+    <n v="118208"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="29"/>
+    <n v="3220"/>
+    <n v="93380"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="41"/>
+    <n v="3295"/>
+    <n v="135095"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="26"/>
+    <n v="2895"/>
+    <n v="75270"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="48"/>
+    <n v="2875"/>
+    <n v="138000"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="38"/>
+    <n v="3485"/>
+    <n v="132430"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="31"/>
+    <n v="2813"/>
+    <n v="87203"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Yes"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <n v="25"/>
+    <n v="2691"/>
+    <n v="67275"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Yes"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <n v="32"/>
+    <n v="3905"/>
+    <n v="124960"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <n v="39"/>
+    <n v="2768"/>
+    <n v="107952"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Yes"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <n v="38"/>
+    <n v="3539"/>
+    <n v="134482"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <n v="46"/>
+    <n v="2767"/>
+    <n v="127282"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <n v="47"/>
+    <n v="3844"/>
+    <n v="180668"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="No"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <n v="30"/>
+    <n v="3240"/>
+    <n v="97200"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Yes"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77A6E0F-4FCB-4DA9-A9E6-5653386B7D39}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Total Profit Ranking">
+  <location ref="A3:C26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="20">
+        <item x="13"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="5"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="5"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="23">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Average of Total Profit" fld="3" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="Average of Profit Per Unit" fld="1" subtotal="average" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="49">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="47">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="4">
+            <x v="1"/>
+            <x v="3"/>
+            <x v="7"/>
+            <x v="16"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="46">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="45">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="4">
+            <x v="2"/>
+            <x v="4"/>
+            <x v="10"/>
+            <x v="15"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="44">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="43">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="4">
+            <x v="0"/>
+            <x v="6"/>
+            <x v="11"/>
+            <x v="17"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="42">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="41">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="7">
+            <x v="5"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="12"/>
+            <x v="13"/>
+            <x v="14"/>
+            <x v="18"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="40">
+      <pivotArea field="5" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,13 +1364,13 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="11">
         <v>48</v>
       </c>
       <c r="C2" s="2">
         <v>3855</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="11">
         <f>B2*C2</f>
         <v>185040</v>
       </c>
@@ -686,13 +1394,13 @@
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="11">
         <v>37</v>
       </c>
       <c r="C3" s="2">
         <v>3672</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="11">
         <f t="shared" ref="D3:D20" si="1">B3*C3</f>
         <v>135864</v>
       </c>
@@ -725,13 +1433,13 @@
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="11">
         <v>43</v>
       </c>
       <c r="C4" s="2">
         <v>3601</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="11">
         <f t="shared" si="1"/>
         <v>154843</v>
       </c>
@@ -765,13 +1473,13 @@
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="11">
         <v>47</v>
       </c>
       <c r="C5" s="2">
         <v>3876</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="11">
         <f t="shared" si="1"/>
         <v>182172</v>
       </c>
@@ -805,13 +1513,13 @@
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="11">
         <v>31</v>
       </c>
       <c r="C6" s="2">
         <v>3446</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="11">
         <f t="shared" si="1"/>
         <v>106826</v>
       </c>
@@ -845,13 +1553,13 @@
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="11">
         <v>32</v>
       </c>
       <c r="C7" s="2">
         <v>3694</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="11">
         <f t="shared" si="1"/>
         <v>118208</v>
       </c>
@@ -880,13 +1588,13 @@
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="11">
         <v>29</v>
       </c>
       <c r="C8" s="2">
         <v>3220</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="11">
         <f t="shared" si="1"/>
         <v>93380</v>
       </c>
@@ -907,13 +1615,13 @@
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="11">
         <v>41</v>
       </c>
       <c r="C9" s="2">
         <v>3295</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="11">
         <f t="shared" si="1"/>
         <v>135095</v>
       </c>
@@ -937,13 +1645,13 @@
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="11">
         <v>26</v>
       </c>
       <c r="C10" s="2">
         <v>2895</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="11">
         <f t="shared" si="1"/>
         <v>75270</v>
       </c>
@@ -976,13 +1684,13 @@
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="11">
         <v>48</v>
       </c>
       <c r="C11" s="2">
         <v>2875</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="11">
         <f t="shared" si="1"/>
         <v>138000</v>
       </c>
@@ -1016,13 +1724,13 @@
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="11">
         <v>38</v>
       </c>
       <c r="C12" s="2">
         <v>3485</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="11">
         <f t="shared" si="1"/>
         <v>132430</v>
       </c>
@@ -1056,13 +1764,13 @@
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="11">
         <v>31</v>
       </c>
       <c r="C13" s="2">
         <v>2813</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="11">
         <f t="shared" si="1"/>
         <v>87203</v>
       </c>
@@ -1096,13 +1804,13 @@
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="11">
         <v>25</v>
       </c>
       <c r="C14" s="2">
         <v>2691</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="11">
         <f t="shared" si="1"/>
         <v>67275</v>
       </c>
@@ -1131,13 +1839,13 @@
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="11">
         <v>32</v>
       </c>
       <c r="C15" s="2">
         <v>3905</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="11">
         <f t="shared" si="1"/>
         <v>124960</v>
       </c>
@@ -1158,13 +1866,13 @@
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="11">
         <v>39</v>
       </c>
       <c r="C16" s="2">
         <v>2768</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="11">
         <f t="shared" si="1"/>
         <v>107952</v>
       </c>
@@ -1185,13 +1893,13 @@
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="11">
         <v>38</v>
       </c>
       <c r="C17" s="2">
         <v>3539</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="11">
         <f t="shared" si="1"/>
         <v>134482</v>
       </c>
@@ -1212,13 +1920,13 @@
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="11">
         <v>46</v>
       </c>
       <c r="C18" s="2">
         <v>2767</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="11">
         <f t="shared" si="1"/>
         <v>127282</v>
       </c>
@@ -1239,13 +1947,13 @@
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="11">
         <v>47</v>
       </c>
       <c r="C19" s="2">
         <v>3844</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="11">
         <f t="shared" si="1"/>
         <v>180668</v>
       </c>
@@ -1266,13 +1974,13 @@
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="11">
         <v>30</v>
       </c>
       <c r="C20" s="2">
         <v>3240</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="11">
         <f t="shared" si="1"/>
         <v>97200</v>
       </c>
@@ -1291,10 +1999,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G20">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="53" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1303,6 +2011,285 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBA111E-F033-4953-92C1-1AB6E9A8C3D6}">
+  <dimension ref="A3:C26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.453125" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="10">
+        <v>175680.75</v>
+      </c>
+      <c r="C4" s="10">
+        <v>46.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="10">
+        <v>185040</v>
+      </c>
+      <c r="C5" s="10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10">
+        <v>182172</v>
+      </c>
+      <c r="C6" s="10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="10">
+        <v>180668</v>
+      </c>
+      <c r="C7" s="10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10">
+        <v>154843</v>
+      </c>
+      <c r="C8" s="10">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="10">
+        <v>135860.25</v>
+      </c>
+      <c r="C9" s="10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10">
+        <v>138000</v>
+      </c>
+      <c r="C10" s="10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="10">
+        <v>135864</v>
+      </c>
+      <c r="C11" s="10">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="10">
+        <v>135095</v>
+      </c>
+      <c r="C12" s="10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="10">
+        <v>134482</v>
+      </c>
+      <c r="C13" s="10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="10">
+        <v>125720</v>
+      </c>
+      <c r="C14" s="10">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10">
+        <v>132430</v>
+      </c>
+      <c r="C15" s="10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="10">
+        <v>127282</v>
+      </c>
+      <c r="C16" s="10">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10">
+        <v>124960</v>
+      </c>
+      <c r="C17" s="10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="10">
+        <v>118208</v>
+      </c>
+      <c r="C18" s="10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="10">
+        <v>90729.428571428565</v>
+      </c>
+      <c r="C19" s="10">
+        <v>30.142857142857142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="10">
+        <v>107952</v>
+      </c>
+      <c r="C20" s="10">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="10">
+        <v>106826</v>
+      </c>
+      <c r="C21" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10">
+        <v>97200</v>
+      </c>
+      <c r="C22" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="10">
+        <v>93380</v>
+      </c>
+      <c r="C23" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="10">
+        <v>87203</v>
+      </c>
+      <c r="C24" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="10">
+        <v>75270</v>
+      </c>
+      <c r="C25" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="10">
+        <v>67275</v>
+      </c>
+      <c r="C26" s="10">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB587DDC-48D0-40B1-82D8-F331944AFEAA}">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1772,11 +2759,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F20">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="52" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",F2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="51" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",F2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
